--- a/reports/monthly_2026_01.xlsx
+++ b/reports/monthly_2026_01.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,7 +86,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A7A4A"/>
+      <color rgb="00C0392B"/>
       <sz val="8"/>
     </font>
     <font>
@@ -116,39 +116,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001B3A6B"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001A1A2E"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00888888"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001A7A4A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00999999"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00FFD700"/>
       <sz val="10"/>
     </font>
@@ -166,6 +133,12 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -192,29 +165,8 @@
       <color rgb="00FFD700"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001A1A1A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001A7A4A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001B3A6B"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -264,16 +216,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000A1929"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF4FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -366,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -436,127 +378,43 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1006,12 +864,12 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Generated: 30 April 2026, 01:00 hrs</t>
+          <t>Generated: 30 April 2026, 01:37 hrs</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Overall Accuracy: 86.67%   |   Avg Processing: 2.0 days</t>
+          <t>Overall Accuracy: 0.0%   |   Avg Processing: 0.0 days</t>
         </is>
       </c>
     </row>
@@ -1044,19 +902,19 @@
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="21" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1">
@@ -1154,341 +1012,81 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>Communication System</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="inlineStr"/>
-      <c r="E14" s="28" t="inlineStr"/>
-      <c r="F14" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="28" t="inlineStr"/>
-      <c r="K14" s="28" t="inlineStr"/>
-      <c r="L14" s="29" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="M14" s="28" t="inlineStr"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="30" t="inlineStr"/>
-      <c r="B15" s="31" t="inlineStr"/>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>Electronic Warfare System</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr"/>
-      <c r="E15" s="33" t="inlineStr"/>
-      <c r="F15" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="35" t="n">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>G R A N D   T O T A L</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr"/>
+      <c r="E14" s="26" t="inlineStr"/>
+      <c r="F14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="33" t="inlineStr"/>
-      <c r="K15" s="33" t="inlineStr"/>
-      <c r="L15" s="34" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M15" s="33" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="25" t="inlineStr"/>
-      <c r="B16" s="36" t="inlineStr"/>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>Fire Control System</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="inlineStr"/>
-      <c r="E16" s="28" t="inlineStr"/>
-      <c r="F16" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="37" t="n">
+      <c r="G14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="28" t="inlineStr"/>
-      <c r="K16" s="28" t="inlineStr"/>
-      <c r="L16" s="29" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M16" s="28" t="inlineStr"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="30" t="inlineStr"/>
-      <c r="B17" s="31" t="inlineStr"/>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr"/>
-      <c r="E17" s="33" t="inlineStr"/>
-      <c r="F17" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="35" t="n">
+      <c r="H14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="33" t="inlineStr"/>
-      <c r="K17" s="33" t="inlineStr"/>
-      <c r="L17" s="34" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M17" s="33" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>Aircraft Engine Subsystem</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr"/>
-      <c r="E18" s="28" t="inlineStr"/>
-      <c r="F18" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="28" t="inlineStr"/>
-      <c r="K18" s="28" t="inlineStr"/>
-      <c r="L18" s="38" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M18" s="28" t="inlineStr"/>
+      <c r="I14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="26" t="inlineStr"/>
+      <c r="K14" s="26" t="inlineStr"/>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr"/>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="27" t="inlineStr"/>
+      <c r="E17" s="27" t="inlineStr"/>
+      <c r="J17" s="27" t="inlineStr"/>
+    </row>
+    <row r="18" ht="35" customHeight="1">
+      <c r="A18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="30" t="inlineStr"/>
-      <c r="B19" s="31" t="inlineStr"/>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>Avionics Module</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr"/>
-      <c r="E19" s="33" t="inlineStr"/>
-      <c r="F19" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="33" t="inlineStr"/>
-      <c r="K19" s="33" t="inlineStr"/>
-      <c r="L19" s="34" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M19" s="33" t="inlineStr"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="25" t="inlineStr"/>
-      <c r="B20" s="36" t="inlineStr"/>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>Helicopter Assembly</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="inlineStr"/>
-      <c r="E20" s="28" t="inlineStr"/>
-      <c r="F20" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="28" t="inlineStr"/>
-      <c r="K20" s="28" t="inlineStr"/>
-      <c r="L20" s="38" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="M20" s="28" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="30" t="inlineStr"/>
-      <c r="B21" s="31" t="inlineStr"/>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr"/>
-      <c r="E21" s="33" t="inlineStr"/>
-      <c r="F21" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="33" t="inlineStr"/>
-      <c r="K21" s="33" t="inlineStr"/>
-      <c r="L21" s="34" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M21" s="33" t="inlineStr"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
-        <is>
-          <t>G R A N D   T O T A L</t>
-        </is>
-      </c>
-      <c r="D22" s="40" t="inlineStr"/>
-      <c r="E22" s="40" t="inlineStr"/>
-      <c r="F22" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="G22" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="H22" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="I22" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="40" t="inlineStr"/>
-      <c r="K22" s="40" t="inlineStr"/>
-      <c r="L22" s="40" t="inlineStr">
-        <is>
-          <t>86.67%</t>
-        </is>
-      </c>
-      <c r="M22" s="40" t="inlineStr"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="41" t="inlineStr"/>
-      <c r="E25" s="41" t="inlineStr"/>
-      <c r="J25" s="41" t="inlineStr"/>
-    </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="42" t="n"/>
-      <c r="E26" s="42" t="n"/>
-      <c r="J26" s="42" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>______________________________</t>
         </is>
       </c>
-      <c r="E27" s="43" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>______________________________</t>
         </is>
       </c>
-      <c r="J27" s="43" t="inlineStr">
+      <c r="J19" s="29" t="inlineStr">
         <is>
           <t>______________________________</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="E28" s="44" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>Checked By / DS Member</t>
         </is>
       </c>
-      <c r="J28" s="44" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>Approved By / Dir Std</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="45" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>DEFENCE STANDARDISATION, BENGALURU  |  Member AC/135  |  Directorate of Standardisation  |  Ministry of Defence, Govt. of India  |  Developed by: Cobra Tech, ABVGIET Shimla</t>
         </is>
@@ -1496,49 +1094,49 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="C3:M3"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="L12:L13"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="E8:I8"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="E17:I17"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="C4:M4"/>
+    <mergeCell ref="E20:I20"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="J17:M17"/>
     <mergeCell ref="J8:M8"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="C1:M1"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="E19:I19"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A30:M30"/>
     <mergeCell ref="A11:M11"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="J28:M28"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="C2:M2"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E27:I27"/>
     <mergeCell ref="A7:M7"/>
-    <mergeCell ref="E26:I26"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D12:E12"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E25:I25"/>
-    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="E18:I18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1550,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1565,7 +1163,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
-      <c r="C1" s="46" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>DIRECTORATE OF STANDARDISATION — BENGALURU</t>
         </is>
@@ -1574,7 +1172,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="1" t="n"/>
-      <c r="C2" s="47" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>CODIFICATION SUMMARY FOR THE MONTH OF JANUARY 2026</t>
         </is>
@@ -1583,127 +1181,73 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
-      <c r="C3" s="48" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>DPSU / AsHSP — WISE CODIFICATION ANALYSIS</t>
         </is>
       </c>
     </row>
     <row r="4" ht="8" customHeight="1">
-      <c r="A4" s="49" t="n"/>
+      <c r="A4" s="35" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>DPSU / AsHSP</t>
         </is>
       </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Total Items</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>NSN Allotted</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Returned</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G5" s="50" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>Accuracy %</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="52" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="C6" s="53" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="53" t="n">
-        <v>14</v>
-      </c>
-      <c r="E6" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="53" t="n">
-        <v>14</v>
-      </c>
-      <c r="G6" s="54" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="C7" s="57" t="n">
-        <v>15</v>
-      </c>
-      <c r="D7" s="57" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="57" t="n">
-        <v>12</v>
-      </c>
-      <c r="G7" s="58" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="G8" s="39" t="inlineStr">
-        <is>
-          <t>86.67%</t>
+      <c r="C6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1256,7 @@
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1725,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1734,69 +1278,30 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>SERVICE-WISE DISTRIBUTION — JANUARY 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="49" t="n"/>
+      <c r="A2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Service / NCB</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>Total Items</t>
         </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="61" t="inlineStr">
-        <is>
-          <t>Airforce</t>
-        </is>
-      </c>
-      <c r="C4" s="62" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="63" t="inlineStr">
-        <is>
-          <t>Army</t>
-        </is>
-      </c>
-      <c r="C5" s="64" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="C6" s="62" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1823,135 +1328,30 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>TOP EQUIPMENT TYPES — JANUARY 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="49" t="n"/>
+      <c r="A2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Equipment Name</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>Items</t>
         </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>🥇</t>
-        </is>
-      </c>
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>Helicopter Assembly</t>
-        </is>
-      </c>
-      <c r="C4" s="62" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>🥈</t>
-        </is>
-      </c>
-      <c r="B5" s="66" t="inlineStr">
-        <is>
-          <t>Communication System</t>
-        </is>
-      </c>
-      <c r="C5" s="64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>🥉</t>
-        </is>
-      </c>
-      <c r="B6" s="65" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="C6" s="62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="66" t="inlineStr">
-        <is>
-          <t>Avionics Module</t>
-        </is>
-      </c>
-      <c r="C7" s="64" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="65" t="inlineStr">
-        <is>
-          <t>Electronic Warfare System</t>
-        </is>
-      </c>
-      <c r="C8" s="62" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="66" t="inlineStr">
-        <is>
-          <t>Aircraft Engine Subsystem</t>
-        </is>
-      </c>
-      <c r="C9" s="64" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="65" t="inlineStr">
-        <is>
-          <t>Fire Control System</t>
-        </is>
-      </c>
-      <c r="C10" s="62" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
